--- a/docs/技术素材.xlsx
+++ b/docs/技术素材.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -660,44 +660,44 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>v3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>7.31</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>F层·+公安部2025术语</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>55.4%</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>35.4%</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>G层·类型确认片段 ★最终版</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>65.2%</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>53.7%</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>0/142</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>注入 44 个公安部反诈关键词</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>大部分无法归入具体类型，无提升，但思路正确</t>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>长词拆 2-3gram + 同类train≥2次确认 + 正常零命中</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>既真实（隔离）又尽量高（短词泛化），用于汇报</t>
         </is>
       </c>
     </row>
@@ -709,37 +709,79 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>G层·类型确认片段 ★最终版</t>
+          <t>G层·类型确认片段 ★回归（数据扩至600/452/800）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>0/142</t>
+          <t>0/241</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>长词拆 2-3gram + 同类train≥2次确认 + 正常零命中</t>
+          <t>模板库补全至v1.5(630/299词) + 图谱同步(1559/1935行)，新词过normal零命中</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>既真实（隔离）又尽量高（短词泛化），用于汇报</t>
+          <t>数据扩后真实泛化提升：ad +4.4pp；生产口径86.0/81.9%（normal扩至800测试面变宽，零误报保持；已统一补贴阈值去掉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>H层·混合分类器（TF-IDF+LR + 关键词救回）★整体最终方案</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>75.6%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5/120 (4.2%)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>分类器(不做类别平衡)为主 + 关键词强命中(score≥3)救回被误判的fraud/ad。train→val选参→test严格流程</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>严格隔离 test：fraud 75.6% / ad 76.5% / 误报4.2%。train→val调参→test 严格流程。含关键词平分bug修复（广告优先）</t>
         </is>
       </c>
     </row>
@@ -757,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -828,12 +870,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>最终正常误报 0/142；strong 词 343 个均经 normal 零命中验证</t>
+          <t>最终正常误报 0/241；strong 词 343 个均经 normal 零命中验证</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>pattern_library v1.4</t>
+          <t>pattern_library v1.5</t>
         </is>
       </c>
     </row>
@@ -858,7 +900,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>naive n-gram 误报 40%+；类型片段误报 0，且召回 +9.8pp/+18.3pp</t>
+          <t>naive n-gram 误报 40%+；类型片段误报 0；G层 val调参后 test 召回 72.2%/64.7%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -873,12 +915,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>七层隔离评测方法论</t>
+          <t>隔离评测方法论（A-E+G 逐层量化泄漏）</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>从「全量无隔离」到「严格隔离」7 层，逐层量化数据泄漏</t>
+          <t>从「全量无隔离」到「严格隔离」逐层量化数据泄漏</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -888,7 +930,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A 63.6% → B 92.1%（泄漏）→ D 55.4%（真实）→ G 65.2%（最终）</t>
+          <t>A 71.3% → B 89.2%（泄漏）→ D 63.3%（真实）→ G 72.2% → H 75.6%（最终）</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -918,7 +960,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>entities.csv 1318 实体，9 类；Brand 286 个广告品牌</t>
+          <t>entities.csv 1559 实体，9 类；Brand 286 个广告品牌</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -948,12 +990,42 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>隔离评测下广告召回 53.7%；泄漏源已标注</t>
+          <t>隔离评测下广告召回 58.1%；泄漏源已标注</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>relations.csv + devlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H层混合仲裁：分类器 + 关键词兜底（最终方案）</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TF-IDF+LR 分类器做主体召回，关键词强命中做二次确认救回</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>分类器擅长语义泛化（召回高），关键词擅长精确零误报（兜底），两者互补</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>严格隔离 test：fraud 75.6% / ad 76.5%（vs 关键词G层72.2%/64.7%）；误报4.2%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>matcher/hybrid_clf.py</t>
         </is>
       </c>
     </row>
@@ -971,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1017,7 +1089,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>368 条 / 28 类</t>
+          <t>600 条 / 28 类</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1039,7 +1111,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>270 条 / 14 类</t>
+          <t>452 条 / 14 类</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1061,12 +1133,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>470 条 / 2 类</t>
+          <t>800 条 / 1 类</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>正常通话（误报测试集）</t>
+          <t>正常通话（误报测试集），8.2 已补银行/运营商/医院/政务场景</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1083,12 +1155,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>28 类 / 479 关键词</t>
+          <t>28类 / 630关键词</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>诈骗模板库 v1.4（含 240 strong）</t>
+          <t>诈骗模板库 v1.5（含343 strong）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1105,12 +1177,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>14 类 / 153 关键词</t>
+          <t>14类 / 299关键词</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>广告模板库 v1.4（含 36 strong）</t>
+          <t>广告模板库 v1.5（含126 strong）</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1127,7 +1199,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1318 行</t>
+          <t>1559行</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1149,7 +1221,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>1675 行</t>
+          <t>1935行</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1180,6 +1252,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>GBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>补充数据_待审/</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fraud232+ad182+normal330</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8.2 补充话术源文件（批次1~8 + 审阅全量），已并入主表</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>GBK</t>
         </is>
@@ -1244,7 +1338,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>✅ 已完成（图谱 + 匹配算法 + 隔离评测）</t>
+          <t>✅ 已完成（数据 600/452/800 + 图谱 + 匹配算法 + 隔离评测）</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1355,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>⏳ 等成员B模型，图谱已就绪</t>
+          <t>⏳ 等成员B模型；数据迭代已完成（fraud 600/ad 452/normal 800），模板库+图谱待同步新数据</t>
         </is>
       </c>
     </row>

--- a/docs/技术素材.xlsx
+++ b/docs/技术素材.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>数据扩后真实泛化提升：ad +4.4pp；生产口径86.0/81.9%（normal扩至800测试面变宽，零误报保持；已统一补贴阈值去掉）</t>
+          <t>数据扩后真实泛化提升：ad +4.4pp；生产口径86.0/81.9%；G层test口径62.2/64.7%（normal隔离修复后）</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,49 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>严格隔离 test：fraud 75.6% / ad 76.5% / 误报4.2%。train→val调参→test 严格流程。含关键词平分bug修复（广告优先）</t>
+          <t>严格隔离 test：fraud 75.6% / ad 76.5% / 误报5/120。train→val调参→test 严格流程。含关键词平分bug修复（广告优先）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v5.1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>H层调参 + 平分规则统一（三脚本）</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85.3%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5/120 (±1 平台波动)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>val误报约束≤3→≤4，选参 C 0.1→0.15；三脚本平分规则统一为「weak命中数优先→广告优先→按类型名排序」确定性规则，消除跨进程哈希依赖</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>test 召回 fraud 75.6→80.0%、ad 76.5→85.3%，误报 5/120（平台波动 ±1：Linux 5/120、Windows 6/120，LR 边界样本 #115 fraud/normal 概率差仅 0.0033）。G层类型准确率 fraud 53.6→58.9%。生产口径 86.0/81.9→85.8/80.8。3-seed 跨进程可复现</t>
         </is>
       </c>
     </row>
@@ -870,7 +912,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>最终正常误报 0/241；strong 词 343 个均经 normal 零命中验证</t>
+          <t>生产口径 matcher.py 正常误报 0/800；strong 词 343 个经 normal 反向筛词（有命中风险的被过滤/降权），G层严格隔离误报 3/120</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -900,7 +942,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>naive n-gram 误报 40%+；类型片段误报 0；G层 val调参后 test 召回 72.2%/64.7%</t>
+          <t>naive n-gram 误报 40%+；类型片段误报 0（train筛）；G层严格隔离 test 召回 62.2%/64.7%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -930,7 +972,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A 71.3% → B 89.2%（泄漏）→ D 63.3%（真实）→ G 72.2% → H 75.6%（最终）</t>
+          <t>A 71.3% → B 89.2%（泄漏）→ D 63.3%（真实）→ G 62.2% → H 80.0%（最终）；normal隔离修复后误报从假0变真3/120</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -960,7 +1002,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>entities.csv 1559 实体，9 类；Brand 286 个广告品牌</t>
+          <t>entities.csv 1559 实体，9 类；Brand 291 个广告品牌</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -990,7 +1032,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>隔离评测下广告召回 58.1%；泄漏源已标注</t>
+          <t>G层严格隔离下广告召回 64.7%；泄漏源已标注</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1020,7 +1062,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>严格隔离 test：fraud 75.6% / ad 76.5%（vs 关键词G层72.2%/64.7%）；误报4.2%</t>
+          <t>严格隔离 test：H层 fraud 80.0%/94.7%/F1 86.7%、ad 85.3%/96.7%/F1 90.6%（全面优于G层62.2%/90.3%/73.7%）；G层仅normal误报更低(3 vs 5~6，平台波动±1)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1253,14 +1295,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>GBK</t>
+          <t>UTF-8 BOM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>补充数据_待审/</t>
+          <t>补充数据（已并入主表）</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1270,7 +1312,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8.2 补充话术源文件（批次1~8 + 审阅全量），已并入主表</t>
+          <t>8.2 补充话术源文件（批次1~8 + 审阅全量），已并入主表，原目录已清理</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/docs/技术素材.xlsx
+++ b/docs/技术素材.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>数据扩后真实泛化提升：ad +4.4pp；生产口径86.0/81.9%（normal扩至800测试面变宽，零误报保持；已统一补贴阈值去掉）</t>
+          <t>数据扩后真实泛化提升：ad +4.4pp；生产口径86.0/81.9%；G层test口径62.2/64.7%（normal隔离修复后）</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,49 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>严格隔离 test：fraud 75.6% / ad 76.5% / 误报4.2%。train→val调参→test 严格流程。含关键词平分bug修复（广告优先）</t>
+          <t>严格隔离 test：fraud 75.6% / ad 76.5% / 误报5/120。train→val调参→test 严格流程。含关键词平分bug修复（广告优先）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v5.1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>H层调参 + 平分规则统一（三脚本）</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85.3%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5/120 (±1 平台波动)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>val误报约束≤3→≤4，选参 C 0.1→0.15；三脚本平分规则统一为「weak命中数优先→广告优先→按类型名排序」确定性规则，消除跨进程哈希依赖</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>test 召回 fraud 75.6→80.0%、ad 76.5→85.3%，误报 5/120（平台波动 ±1：Linux 5/120、Windows 6/120，LR 边界样本 #115 fraud/normal 概率差仅 0.0033）。G层类型准确率 fraud 53.6→58.9%。生产口径 86.0/81.9→85.8/80.8。3-seed 跨进程可复现</t>
         </is>
       </c>
     </row>
@@ -870,7 +912,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>最终正常误报 0/241；strong 词 343 个均经 normal 零命中验证</t>
+          <t>生产口径 matcher.py（B层·indicates全表）正常误报 22/800；strong 词 343 个经 normal 反向筛词（有命中风险的被过滤/降权），G层严格隔离误报 3/120</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -900,7 +942,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>naive n-gram 误报 40%+；类型片段误报 0；G层 val调参后 test 召回 72.2%/64.7%</t>
+          <t>naive n-gram 误报 40%+；类型片段误报 0（train筛）；G层严格隔离 test 召回 62.2%/64.7%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -930,7 +972,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A 71.3% → B 89.2%（泄漏）→ D 63.3%（真实）→ G 72.2% → H 75.6%（最终）</t>
+          <t>A 71.3% → B 89.2%（泄漏）→ D 63.3%（真实）→ G 62.2% → H 80.0%（最终）；normal隔离修复后误报从假0变真3/120</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -960,7 +1002,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>entities.csv 1559 实体，9 类；Brand 286 个广告品牌</t>
+          <t>entities.csv 1559 实体，9 类；Brand 291 个广告品牌</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -990,7 +1032,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>隔离评测下广告召回 58.1%；泄漏源已标注</t>
+          <t>G层严格隔离下广告召回 64.7%；泄漏源已标注</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1020,7 +1062,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>严格隔离 test：fraud 75.6% / ad 76.5%（vs 关键词G层72.2%/64.7%）；误报4.2%</t>
+          <t>严格隔离 test：H层 fraud 80.0%/94.7%/F1 86.7%、ad 85.3%/96.7%/F1 90.6%（全面优于G层62.2%/90.3%/73.7%）；G层仅normal误报更低(3 vs 5~6，平台波动±1)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1253,14 +1295,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>GBK</t>
+          <t>UTF-8 BOM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>补充数据_待审/</t>
+          <t>补充数据（已并入主表）</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1270,7 +1312,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8.2 补充话术源文件（批次1~8 + 审阅全量），已并入主表</t>
+          <t>8.2 补充话术源文件（批次1~8 + 审阅全量），已并入主表，原目录已清理</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
